--- a/DATA/10_bank_events.xlsx
+++ b/DATA/10_bank_events.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,26 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,29 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -551,7 +524,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Significantly expanded asset base, paid-up capital and branch network across Nepal.</t>
+          <t>Expanded asset base, paid-up capital and branch network.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -611,7 +584,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Expanded retail deposit base, branch footprint, and consolidated market leadership in balance sheet size.</t>
+          <t>Expanded retail deposit base, branch footprint.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -671,7 +644,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Created the largest commercial bank in Nepal by capital fund, asset size, and total deposits.</t>
+          <t>Created largest commercial bank by capital fund and asset size.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -776,7 +749,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Merger between Nepal Investment Bank Ltd (NIBL) and Mega Bank Nepal Ltd</t>
+          <t>Merger of NIBL and Mega Bank Nepal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -791,7 +764,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Substantial capital boost, combined corporate lending power and retail branch strength.</t>
+          <t>Substantial capital boost, combined corporate and retail strength.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -851,7 +824,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Strengthened capital base, improved liquidity buffer, and broadened suburban outreach.</t>
+          <t>Strengthened capital base, improved liquidity buffer.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -911,7 +884,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Strengthened market share in Tier 2/3 cities and expanded SME lending portfolio.</t>
+          <t>Strengthened market share in Tier 2/3 cities.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -956,7 +929,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Merger between Laxmi Bank Limited and Sunrise Bank Limited</t>
+          <t>Merger between Laxmi Bank and Sunrise Bank</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -971,7 +944,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Consolidated balance sheet over NPR 300 billion with unified digital banking infrastructure.</t>
+          <t>Consolidated balance sheet over NPR 300 billion.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -981,7 +954,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Swap ratio 1:1, commenced joint operation at start of FY2024.</t>
+          <t>Swap ratio 1:1, commenced FY2024.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1004,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Drove massive retail customer acquisition and digital transaction volume growth.</t>
+          <t>Drove massive retail customer acquisition.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1041,7 +1014,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Pioneered paperless branch customer service in Nepal.</t>
+          <t>Pioneered paperless branch service in Nepal.</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1064,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Maintained dominant fee-income market share in multinational and institutional cash management.</t>
+          <t>Maintained dominant fee-income market share.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1101,7 +1074,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Corporate and institutional digital cash management.</t>
+          <t>Corporate digital cash management.</t>
         </is>
       </c>
     </row>
